--- a/baselines/BASELINE_v9_WC_GL.xlsx
+++ b/baselines/BASELINE_v9_WC_GL.xlsx
@@ -399,1530 +399,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E89"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Metric</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Year 1 / 2026</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Year 2 / 2027</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Year 3 / 2028</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Year</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Year Number</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Year</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Calendar Year</v>
-      </c>
-      <c r="C3">
-        <v>2026</v>
-      </c>
-      <c r="D3">
-        <v>2027</v>
-      </c>
-      <c r="E3">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Rate Change</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Funding Confidence Level</v>
-      </c>
-      <c r="C5">
-        <v>0.75</v>
-      </c>
-      <c r="D5">
-        <v>0.75</v>
-      </c>
-      <c r="E5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Selected CLF</v>
-      </c>
-      <c r="C6">
-        <v>1.346</v>
-      </c>
-      <c r="D6">
-        <v>1.346</v>
-      </c>
-      <c r="E6">
-        <v>1.346</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Dividend %</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Assessment %</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Underwriting Strictness</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Risk Control %</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Decisions</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Reinsurance Level</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Active Members</v>
-      </c>
-      <c r="C12">
-        <v>62</v>
-      </c>
-      <c r="D12">
-        <v>63</v>
-      </c>
-      <c r="E12">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B13" t="str">
-        <v>New Members</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Withdrawn Members</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Member Retention Rate</v>
-      </c>
-      <c r="C15">
-        <v>0.967</v>
-      </c>
-      <c r="D15">
-        <v>0.968</v>
-      </c>
-      <c r="E15">
-        <v>0.952</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Member Satisfaction</v>
-      </c>
-      <c r="C16">
-        <v>7.674193548387098</v>
-      </c>
-      <c r="D16">
-        <v>7.677777777777779</v>
-      </c>
-      <c r="E16">
-        <v>7.68125</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Average Risk Quality</v>
-      </c>
-      <c r="C17">
-        <v>5.096774193548387</v>
-      </c>
-      <c r="D17">
-        <v>5.0888888888888895</v>
-      </c>
-      <c r="E17">
-        <v>5.08125</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Active Exposure — WC (Payroll $M)</v>
-      </c>
-      <c r="C18">
-        <v>66.24</v>
-      </c>
-      <c r="D18">
-        <v>66.24</v>
-      </c>
-      <c r="E18">
-        <v>66.24</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Active Exposure — GL (Payroll $M)</v>
-      </c>
-      <c r="C19">
-        <v>86.15</v>
-      </c>
-      <c r="D19">
-        <v>88.25</v>
-      </c>
-      <c r="E19">
-        <v>87.07</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Total Market Exposure — WC (Payroll $M)</v>
-      </c>
-      <c r="C20">
-        <v>66.24</v>
-      </c>
-      <c r="D20">
-        <v>66.24</v>
-      </c>
-      <c r="E20">
-        <v>66.24</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Total Market Exposure — GL (Payroll $M)</v>
-      </c>
-      <c r="C21">
-        <v>66.24</v>
-      </c>
-      <c r="D21">
-        <v>66.24</v>
-      </c>
-      <c r="E21">
-        <v>66.24</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Market Share — WC</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Membership</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Market Share — GL</v>
-      </c>
-      <c r="C23">
-        <v>1.3006</v>
-      </c>
-      <c r="D23">
-        <v>1.3323</v>
-      </c>
-      <c r="E23">
-        <v>1.3145</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Rate Level Index</v>
-      </c>
-      <c r="C24">
-        <v>100</v>
-      </c>
-      <c r="D24">
-        <v>100</v>
-      </c>
-      <c r="E24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Pure Premium Rate per $100 Payroll</v>
-      </c>
-      <c r="C25">
-        <v>8.9738</v>
-      </c>
-      <c r="D25">
-        <v>9.473</v>
-      </c>
-      <c r="E25">
-        <v>9.9999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Pool Premium Rate at Selected CLF</v>
-      </c>
-      <c r="C26">
-        <v>13.71303894103304</v>
-      </c>
-      <c r="D26">
-        <v>14.493907240168035</v>
-      </c>
-      <c r="E26">
-        <v>15.289550637511383</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Gross Premium &amp; Admin Expense Rate per $100</v>
-      </c>
-      <c r="C27">
-        <v>17.8335</v>
-      </c>
-      <c r="D27">
-        <v>18.8255</v>
-      </c>
-      <c r="E27">
-        <v>19.8728</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Written Exposure — WC (Payroll $M)</v>
-      </c>
-      <c r="C28">
-        <v>66.24</v>
-      </c>
-      <c r="D28">
-        <v>66.24</v>
-      </c>
-      <c r="E28">
-        <v>66.24</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Written Exposure — GL (Payroll $M)</v>
-      </c>
-      <c r="C29">
-        <v>86.15</v>
-      </c>
-      <c r="D29">
-        <v>88.25</v>
-      </c>
-      <c r="E29">
-        <v>87.07</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Pure Premium</v>
-      </c>
-      <c r="C30">
-        <v>15525483</v>
-      </c>
-      <c r="D30">
-        <v>16635689</v>
-      </c>
-      <c r="E30">
-        <v>17414866</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Pool Premium at Selected CLF</v>
-      </c>
-      <c r="C31">
-        <v>20897300</v>
-      </c>
-      <c r="D31">
-        <v>22391637</v>
-      </c>
-      <c r="E31">
-        <v>23440410</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Admin Expense</v>
-      </c>
-      <c r="C32">
-        <v>2328822</v>
-      </c>
-      <c r="D32">
-        <v>2495353</v>
-      </c>
-      <c r="E32">
-        <v>2612230</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Gross Premium &amp; Admin Expense</v>
-      </c>
-      <c r="C33">
-        <v>30853637</v>
-      </c>
-      <c r="D33">
-        <v>33059938</v>
-      </c>
-      <c r="E33">
-        <v>34608390</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Assessments</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Rate and Premium</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Dividends / Returned Pool Premium</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Pure Premium</v>
-      </c>
-      <c r="C36">
-        <v>15525483</v>
-      </c>
-      <c r="D36">
-        <v>16635689</v>
-      </c>
-      <c r="E36">
-        <v>17414866</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Pool Premium at Selected CLF</v>
-      </c>
-      <c r="C37">
-        <v>20897300</v>
-      </c>
-      <c r="D37">
-        <v>22391637</v>
-      </c>
-      <c r="E37">
-        <v>23440410</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Member-Level Simulated Loss incl. Shared Events</v>
-      </c>
-      <c r="C38">
-        <v>19797369</v>
-      </c>
-      <c r="D38">
-        <v>16205013</v>
-      </c>
-      <c r="E38">
-        <v>13092179</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Shared Annual Loss Factor</v>
-      </c>
-      <c r="C39">
-        <v>1.238702373877127</v>
-      </c>
-      <c r="D39">
-        <v>1.170480370297434</v>
-      </c>
-      <c r="E39">
-        <v>0.841846483201276</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Catastrophe Factor</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Shock Uplift (included in simulated loss)</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Gross Ultimate Loss + LAE</v>
-      </c>
-      <c r="C42">
-        <v>19797369</v>
-      </c>
-      <c r="D42">
-        <v>16205013</v>
-      </c>
-      <c r="E42">
-        <v>13092179</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Shock Loss Incurred</v>
-      </c>
-      <c r="C43" t="str">
-        <v>No</v>
-      </c>
-      <c r="D43" t="str">
-        <v>No</v>
-      </c>
-      <c r="E43" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Reinsurance Recovery</v>
-      </c>
-      <c r="C44">
-        <v>1679365</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Losses</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Net Ultimate Loss + LAE</v>
-      </c>
-      <c r="C45">
-        <v>18118004</v>
-      </c>
-      <c r="D45">
-        <v>16205013</v>
-      </c>
-      <c r="E45">
-        <v>13092179</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Operating Expense</v>
-      </c>
-      <c r="C46">
-        <v>2328822</v>
-      </c>
-      <c r="D46">
-        <v>2495353</v>
-      </c>
-      <c r="E46">
-        <v>2612230</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Risk Control Investment</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Reinsurance Cost</v>
-      </c>
-      <c r="C48">
-        <v>7836488</v>
-      </c>
-      <c r="D48">
-        <v>8396864</v>
-      </c>
-      <c r="E48">
-        <v>8790154</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Invested Assets</v>
-      </c>
-      <c r="C49">
-        <v>40202154</v>
-      </c>
-      <c r="D49">
-        <v>46681431</v>
-      </c>
-      <c r="E49">
-        <v>58853678</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Investment Return Rate</v>
-      </c>
-      <c r="C50">
-        <v>-0.00815269779470125</v>
-      </c>
-      <c r="D50">
-        <v>0.10278529887701068</v>
-      </c>
-      <c r="E50">
-        <v>0.05880652318289086</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Investment Income</v>
-      </c>
-      <c r="C51">
-        <v>-327756</v>
-      </c>
-      <c r="D51">
-        <v>4798165</v>
-      </c>
-      <c r="E51">
-        <v>3460980</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Expenses and Income</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Net Income</v>
-      </c>
-      <c r="C52">
-        <v>1767646</v>
-      </c>
-      <c r="D52">
-        <v>10252799</v>
-      </c>
-      <c r="E52">
-        <v>13229199</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Prior-Year Development</v>
-      </c>
-      <c r="C53">
-        <v>-474922</v>
-      </c>
-      <c r="D53">
-        <v>-508073</v>
-      </c>
-      <c r="E53">
-        <v>-345608</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Beginning Gross Reserve</v>
-      </c>
-      <c r="C54">
-        <v>NaN</v>
-      </c>
-      <c r="D54">
-        <v>NaN</v>
-      </c>
-      <c r="E54">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Current-Year Gross Reserve</v>
-      </c>
-      <c r="C55">
-        <v>NaN</v>
-      </c>
-      <c r="D55">
-        <v>NaN</v>
-      </c>
-      <c r="E55">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Gross Paid Losses</v>
-      </c>
-      <c r="C56">
-        <v>NaN</v>
-      </c>
-      <c r="D56">
-        <v>NaN</v>
-      </c>
-      <c r="E56">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Ending Gross Reserve</v>
-      </c>
-      <c r="C57">
-        <v>NaN</v>
-      </c>
-      <c r="D57">
-        <v>NaN</v>
-      </c>
-      <c r="E57">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Beginning RI Recoverable</v>
-      </c>
-      <c r="C58">
-        <v>NaN</v>
-      </c>
-      <c r="D58">
-        <v>NaN</v>
-      </c>
-      <c r="E58">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Ending RI Recoverable</v>
-      </c>
-      <c r="C59">
-        <v>NaN</v>
-      </c>
-      <c r="D59">
-        <v>NaN</v>
-      </c>
-      <c r="E59">
-        <v>NaN</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Expected Net Unpaid Loss</v>
-      </c>
-      <c r="C60">
-        <v>22293895</v>
-      </c>
-      <c r="D60">
-        <v>24544287</v>
-      </c>
-      <c r="E60">
-        <v>24033739</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
-      </c>
-      <c r="C61">
-        <v>30007583</v>
-      </c>
-      <c r="D61">
-        <v>33036611</v>
-      </c>
-      <c r="E61">
-        <v>32349413</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Reserves</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Reserve Risk Margin Needed</v>
-      </c>
-      <c r="C62">
-        <v>21201494</v>
-      </c>
-      <c r="D62">
-        <v>23341617</v>
-      </c>
-      <c r="E62">
-        <v>22856086</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Beginning Cash</v>
-      </c>
-      <c r="C63">
-        <v>4144849</v>
-      </c>
-      <c r="D63">
-        <v>4628046</v>
-      </c>
-      <c r="E63">
-        <v>4958991</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Ending Cash</v>
-      </c>
-      <c r="C64">
-        <v>4628046</v>
-      </c>
-      <c r="D64">
-        <v>4958991</v>
-      </c>
-      <c r="E64">
-        <v>5191258</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Beginning Investments</v>
-      </c>
-      <c r="C65">
-        <v>40202154</v>
-      </c>
-      <c r="D65">
-        <v>46681431</v>
-      </c>
-      <c r="E65">
-        <v>58853678</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Ending Investments</v>
-      </c>
-      <c r="C66">
-        <v>46681431</v>
-      </c>
-      <c r="D66">
-        <v>58853678</v>
-      </c>
-      <c r="E66">
-        <v>71340061</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Other Assets</v>
-      </c>
-      <c r="C67">
-        <v>507083</v>
-      </c>
-      <c r="D67">
-        <v>507083</v>
-      </c>
-      <c r="E67">
-        <v>507083</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Total Assets</v>
-      </c>
-      <c r="C68">
-        <v>51816559</v>
-      </c>
-      <c r="D68">
-        <v>64319751</v>
-      </c>
-      <c r="E68">
-        <v>77038402</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Unearned Premium</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Other Liabilities</v>
-      </c>
-      <c r="C70">
-        <v>392736</v>
-      </c>
-      <c r="D70">
-        <v>392736</v>
-      </c>
-      <c r="E70">
-        <v>392736</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Total Liabilities</v>
-      </c>
-      <c r="C71">
-        <v>22686631</v>
-      </c>
-      <c r="D71">
-        <v>24937024</v>
-      </c>
-      <c r="E71">
-        <v>24426476</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Beginning Surplus</v>
-      </c>
-      <c r="C72">
-        <v>27362282</v>
-      </c>
-      <c r="D72">
-        <v>29129928</v>
-      </c>
-      <c r="E72">
-        <v>39382727</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Surplus from Income</v>
-      </c>
-      <c r="C73">
-        <v>29129928</v>
-      </c>
-      <c r="D73">
-        <v>39382727</v>
-      </c>
-      <c r="E73">
-        <v>52611927</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Ending Surplus</v>
-      </c>
-      <c r="C74">
-        <v>29129928</v>
-      </c>
-      <c r="D74">
-        <v>39382727</v>
-      </c>
-      <c r="E74">
-        <v>52611927</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Balance Sheet and Surplus</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Surplus Tie-Out Difference</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Inter-Line Loan</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Loan Originated This Year</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Inter-Line Loan</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Loan Interest Accrued</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Inter-Line Loan</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Loan Repayment Applied</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Inter-Line Loan</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Outstanding Loan Balance</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Expected Loss Ratio</v>
-      </c>
-      <c r="C80">
-        <v>0.6684491978609625</v>
-      </c>
-      <c r="D80">
-        <v>0.6684491978609626</v>
-      </c>
-      <c r="E80">
-        <v>0.6684491978609626</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Expected Expense Ratio</v>
-      </c>
-      <c r="C81">
-        <v>0.33155080213903754</v>
-      </c>
-      <c r="D81">
-        <v>0.3315508021390374</v>
-      </c>
-      <c r="E81">
-        <v>0.3315508021390374</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Expected Combined Ratio</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Actual Loss Ratio</v>
-      </c>
-      <c r="C83">
-        <v>0.602616976221083</v>
-      </c>
-      <c r="D83">
-        <v>0.5055389508243922</v>
-      </c>
-      <c r="E83">
-        <v>0.38828119055952354</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Actual Expense Ratio</v>
-      </c>
-      <c r="C84">
-        <v>0.3294687740591458</v>
-      </c>
-      <c r="D84">
-        <v>0.3294687740591459</v>
-      </c>
-      <c r="E84">
-        <v>0.3294687740591459</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Actual Combined Ratio</v>
-      </c>
-      <c r="C85">
-        <v>0.9320857502802289</v>
-      </c>
-      <c r="D85">
-        <v>0.835007724883538</v>
-      </c>
-      <c r="E85">
-        <v>0.7177499646186694</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Surplus</v>
-      </c>
-      <c r="C86">
-        <v>29129928</v>
-      </c>
-      <c r="D86">
-        <v>39382727</v>
-      </c>
-      <c r="E86">
-        <v>52611927</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C87">
-        <v>7928434</v>
-      </c>
-      <c r="D87">
-        <v>16041110</v>
-      </c>
-      <c r="E87">
-        <v>29755841</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C88">
-        <v>0.37395636433843166</v>
-      </c>
-      <c r="D88">
-        <v>0.687232153357253</v>
-      </c>
-      <c r="E88">
-        <v>1.3018782195620995</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Excess Capital Status</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Strong</v>
-      </c>
-      <c r="D89" t="str">
-        <v>Strong</v>
-      </c>
-      <c r="E89" t="str">
-        <v>Strong</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E89"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E87"/>
   <sheetData>
     <row r="1">
@@ -2114,19 +590,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decisions</v>
+        <v>Membership</v>
       </c>
       <c r="B12" t="str">
-        <v>Asset Allocation</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Cash 10% / Bonds 80% / Equities 10%</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Cash 10% / Bonds 80% / Equities 10%</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Cash 10% / Bonds 80% / Equities 10%</v>
+        <v>Active Members</v>
+      </c>
+      <c r="C12">
+        <v>62</v>
+      </c>
+      <c r="D12">
+        <v>63</v>
+      </c>
+      <c r="E12">
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -2134,16 +610,16 @@
         <v>Membership</v>
       </c>
       <c r="B13" t="str">
-        <v>Active Members</v>
+        <v>New Members</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2151,16 +627,16 @@
         <v>Membership</v>
       </c>
       <c r="B14" t="str">
-        <v>New Members</v>
+        <v>Withdrawn Members</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2168,16 +644,16 @@
         <v>Membership</v>
       </c>
       <c r="B15" t="str">
-        <v>Withdrawn Members</v>
+        <v>Member Retention Rate</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0.968</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="16">
@@ -2185,16 +661,16 @@
         <v>Membership</v>
       </c>
       <c r="B16" t="str">
-        <v>Member Retention Rate</v>
+        <v>Member Satisfaction</v>
       </c>
       <c r="C16">
-        <v>0.964</v>
+        <v>7.674193548387098</v>
       </c>
       <c r="D16">
-        <v>0.964</v>
+        <v>7.677777777777779</v>
       </c>
       <c r="E16">
-        <v>0.964</v>
+        <v>7.68125</v>
       </c>
     </row>
     <row r="17">
@@ -2202,16 +678,16 @@
         <v>Membership</v>
       </c>
       <c r="B17" t="str">
-        <v>Member Satisfaction</v>
+        <v>Average Risk Quality</v>
       </c>
       <c r="C17">
-        <v>7.4</v>
+        <v>5.096774193548387</v>
       </c>
       <c r="D17">
-        <v>7.4</v>
+        <v>5.0888888888888895</v>
       </c>
       <c r="E17">
-        <v>7.4</v>
+        <v>5.08125</v>
       </c>
     </row>
     <row r="18">
@@ -2219,16 +695,16 @@
         <v>Membership</v>
       </c>
       <c r="B18" t="str">
-        <v>Average Risk Quality</v>
+        <v>Active Exposure — WC (Payroll $M)</v>
       </c>
       <c r="C18">
-        <v>5.7</v>
+        <v>66.24</v>
       </c>
       <c r="D18">
-        <v>5.7</v>
+        <v>66.24</v>
       </c>
       <c r="E18">
-        <v>5.7</v>
+        <v>66.24</v>
       </c>
     </row>
     <row r="19">
@@ -2236,16 +712,16 @@
         <v>Membership</v>
       </c>
       <c r="B19" t="str">
-        <v>Exposure Basis</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Payroll ($M)</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Payroll ($M)</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Payroll ($M)</v>
+        <v>Active Exposure — GL (Payroll $M)</v>
+      </c>
+      <c r="C19">
+        <v>86.15</v>
+      </c>
+      <c r="D19">
+        <v>88.25</v>
+      </c>
+      <c r="E19">
+        <v>87.07</v>
       </c>
     </row>
     <row r="20">
@@ -2253,7 +729,7 @@
         <v>Membership</v>
       </c>
       <c r="B20" t="str">
-        <v>Active Payroll Exposure ($M)</v>
+        <v>Total Market Exposure — WC (Payroll $M)</v>
       </c>
       <c r="C20">
         <v>66.24</v>
@@ -2270,7 +746,7 @@
         <v>Membership</v>
       </c>
       <c r="B21" t="str">
-        <v>Total Market Payroll ($M)</v>
+        <v>Total Market Exposure — GL (Payroll $M)</v>
       </c>
       <c r="C21">
         <v>66.24</v>
@@ -2287,7 +763,7 @@
         <v>Membership</v>
       </c>
       <c r="B22" t="str">
-        <v>Market Share</v>
+        <v>Market Share — WC</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2301,19 +777,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Rate and Premium</v>
+        <v>Membership</v>
       </c>
       <c r="B23" t="str">
-        <v>Rate Level Index</v>
+        <v>Market Share — GL</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>1.3006</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>1.3323</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>1.3145</v>
       </c>
     </row>
     <row r="24">
@@ -2321,16 +797,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B24" t="str">
-        <v>Pure Premium Rate per $100 Payroll</v>
+        <v>Rate Level Index</v>
       </c>
       <c r="C24">
-        <v>8.9738</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>9.473</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>9.9999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -2338,16 +814,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B25" t="str">
-        <v>Pool Premium Rate at Selected CLF</v>
+        <v>Pure Premium Rate per $100 Payroll</v>
       </c>
       <c r="C25">
-        <v>12.07868926280107</v>
+        <v>8.9738</v>
       </c>
       <c r="D25">
-        <v>12.75060921972499</v>
+        <v>9.473</v>
       </c>
       <c r="E25">
-        <v>13.459907108864044</v>
+        <v>9.9999</v>
       </c>
     </row>
     <row r="26">
@@ -2355,16 +831,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B26" t="str">
-        <v>Gross Premium &amp; Admin Expense Rate per $100</v>
+        <v>Pool Premium Rate at Selected CLF</v>
       </c>
       <c r="C26">
-        <v>17.8335</v>
+        <v>13.71303894103304</v>
       </c>
       <c r="D26">
-        <v>18.8255</v>
+        <v>14.493907240168035</v>
       </c>
       <c r="E26">
-        <v>19.8728</v>
+        <v>15.289550637511383</v>
       </c>
     </row>
     <row r="27">
@@ -2372,16 +848,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B27" t="str">
-        <v>Written Payroll ($M)</v>
+        <v>Gross Premium &amp; Admin Expense Rate per $100</v>
       </c>
       <c r="C27">
-        <v>66.24</v>
+        <v>17.8335</v>
       </c>
       <c r="D27">
-        <v>66.24</v>
+        <v>18.8255</v>
       </c>
       <c r="E27">
-        <v>66.24</v>
+        <v>19.8728</v>
       </c>
     </row>
     <row r="28">
@@ -2389,16 +865,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B28" t="str">
-        <v>Pure Premium</v>
+        <v>Written Exposure — WC (Payroll $M)</v>
       </c>
       <c r="C28">
-        <v>5944223</v>
+        <v>66.24</v>
       </c>
       <c r="D28">
-        <v>6274891</v>
+        <v>66.24</v>
       </c>
       <c r="E28">
-        <v>6623954</v>
+        <v>66.24</v>
       </c>
     </row>
     <row r="29">
@@ -2406,16 +882,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B29" t="str">
-        <v>Pool Premium at Selected CLF</v>
+        <v>Written Exposure — GL (Payroll $M)</v>
       </c>
       <c r="C29">
-        <v>8000924</v>
+        <v>86.15</v>
       </c>
       <c r="D29">
-        <v>8446004</v>
+        <v>88.25</v>
       </c>
       <c r="E29">
-        <v>8915842</v>
+        <v>87.07</v>
       </c>
     </row>
     <row r="30">
@@ -2423,16 +899,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B30" t="str">
-        <v>Admin Expense</v>
+        <v>Pure Premium</v>
       </c>
       <c r="C30">
-        <v>891633</v>
+        <v>15525483</v>
       </c>
       <c r="D30">
-        <v>941234</v>
+        <v>16635689</v>
       </c>
       <c r="E30">
-        <v>993593</v>
+        <v>17414866</v>
       </c>
     </row>
     <row r="31">
@@ -2440,16 +916,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B31" t="str">
-        <v>Gross Premium &amp; Admin Expense</v>
+        <v>Pool Premium at Selected CLF</v>
       </c>
       <c r="C31">
-        <v>11812894</v>
+        <v>20897300</v>
       </c>
       <c r="D31">
-        <v>12470029</v>
+        <v>22391637</v>
       </c>
       <c r="E31">
-        <v>13163718</v>
+        <v>23440410</v>
       </c>
     </row>
     <row r="32">
@@ -2457,16 +933,16 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B32" t="str">
-        <v>Assessments</v>
+        <v>Admin Expense</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>2328822</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2495353</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2612230</v>
       </c>
     </row>
     <row r="33">
@@ -2474,50 +950,50 @@
         <v>Rate and Premium</v>
       </c>
       <c r="B33" t="str">
-        <v>Dividends / Returned Pool Premium</v>
+        <v>Gross Premium &amp; Admin Expense</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>30853637</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>33059938</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>34608390</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Losses</v>
+        <v>Rate and Premium</v>
       </c>
       <c r="B34" t="str">
-        <v>Pure Premium</v>
+        <v>Assessments</v>
       </c>
       <c r="C34">
-        <v>5944223</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>6274891</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>6623954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Losses</v>
+        <v>Rate and Premium</v>
       </c>
       <c r="B35" t="str">
-        <v>Pool Premium at Selected CLF</v>
+        <v>Dividends / Returned Pool Premium</v>
       </c>
       <c r="C35">
-        <v>8000924</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>8446004</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>8915842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2525,16 +1001,16 @@
         <v>Losses</v>
       </c>
       <c r="B36" t="str">
-        <v>Member-Level Simulated Loss incl. Shared Events</v>
+        <v>Pure Premium</v>
       </c>
       <c r="C36">
-        <v>5581640</v>
+        <v>15525483</v>
       </c>
       <c r="D36">
-        <v>6073469</v>
+        <v>16635689</v>
       </c>
       <c r="E36">
-        <v>7158788</v>
+        <v>17414866</v>
       </c>
     </row>
     <row r="37">
@@ -2542,16 +1018,16 @@
         <v>Losses</v>
       </c>
       <c r="B37" t="str">
-        <v>Shared Annual Loss Factor</v>
+        <v>Pool Premium at Selected CLF</v>
       </c>
       <c r="C37">
-        <v>1.1049503865330403</v>
+        <v>20897300</v>
       </c>
       <c r="D37">
-        <v>1.1103116094116727</v>
+        <v>22391637</v>
       </c>
       <c r="E37">
-        <v>1.0060010545881324</v>
+        <v>23440410</v>
       </c>
     </row>
     <row r="38">
@@ -2559,16 +1035,16 @@
         <v>Losses</v>
       </c>
       <c r="B38" t="str">
-        <v>Catastrophe Factor</v>
+        <v>Member-Level Simulated Loss incl. Shared Events</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>19797369</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>16205013</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>13092179</v>
       </c>
     </row>
     <row r="39">
@@ -2576,16 +1052,16 @@
         <v>Losses</v>
       </c>
       <c r="B39" t="str">
-        <v>Shock Uplift (included in simulated loss)</v>
+        <v>Shared Annual Loss Factor</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1.238702373877127</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1.170480370297434</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.841846483201276</v>
       </c>
     </row>
     <row r="40">
@@ -2593,16 +1069,16 @@
         <v>Losses</v>
       </c>
       <c r="B40" t="str">
-        <v>Gross Ultimate Loss + LAE</v>
+        <v>Catastrophe Factor</v>
       </c>
       <c r="C40">
-        <v>5581640</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>6073469</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>7158788</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2610,16 +1086,16 @@
         <v>Losses</v>
       </c>
       <c r="B41" t="str">
-        <v>Shock Loss Incurred</v>
-      </c>
-      <c r="C41" t="str">
-        <v>No</v>
-      </c>
-      <c r="D41" t="str">
-        <v>No</v>
-      </c>
-      <c r="E41" t="str">
-        <v>No</v>
+        <v>Shock Uplift (included in simulated loss)</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2627,16 +1103,16 @@
         <v>Losses</v>
       </c>
       <c r="B42" t="str">
-        <v>Reinsurance Recovery</v>
+        <v>Gross Ultimate Loss + LAE</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>19797369</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>16205013</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>13092179</v>
       </c>
     </row>
     <row r="43">
@@ -2644,50 +1120,50 @@
         <v>Losses</v>
       </c>
       <c r="B43" t="str">
-        <v>Net Ultimate Loss + LAE</v>
-      </c>
-      <c r="C43">
-        <v>5581640</v>
-      </c>
-      <c r="D43">
-        <v>6073469</v>
-      </c>
-      <c r="E43">
-        <v>7158788</v>
+        <v>Shock Loss Incurred</v>
+      </c>
+      <c r="C43" t="str">
+        <v>No</v>
+      </c>
+      <c r="D43" t="str">
+        <v>No</v>
+      </c>
+      <c r="E43" t="str">
+        <v>No</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Expenses and Income</v>
+        <v>Losses</v>
       </c>
       <c r="B44" t="str">
-        <v>Operating Expense</v>
+        <v>Reinsurance Recovery</v>
       </c>
       <c r="C44">
-        <v>891633</v>
+        <v>1679365</v>
       </c>
       <c r="D44">
-        <v>941234</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>993593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Expenses and Income</v>
+        <v>Losses</v>
       </c>
       <c r="B45" t="str">
-        <v>Risk Control Investment</v>
+        <v>Net Ultimate Loss + LAE</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>18118004</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>16205013</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>13092179</v>
       </c>
     </row>
     <row r="46">
@@ -2695,16 +1171,16 @@
         <v>Expenses and Income</v>
       </c>
       <c r="B46" t="str">
-        <v>Reinsurance Cost</v>
+        <v>Operating Expense</v>
       </c>
       <c r="C46">
-        <v>3000346</v>
+        <v>2328822</v>
       </c>
       <c r="D46">
-        <v>3167251</v>
+        <v>2495353</v>
       </c>
       <c r="E46">
-        <v>3343441</v>
+        <v>2612230</v>
       </c>
     </row>
     <row r="47">
@@ -2712,16 +1188,16 @@
         <v>Expenses and Income</v>
       </c>
       <c r="B47" t="str">
-        <v>Invested Assets</v>
+        <v>Risk Control Investment</v>
       </c>
       <c r="C47">
-        <v>18597505</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>21262826</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>26236146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2729,16 +1205,16 @@
         <v>Expenses and Income</v>
       </c>
       <c r="B48" t="str">
-        <v>Investment Return Rate</v>
+        <v>Reinsurance Cost</v>
       </c>
       <c r="C48">
-        <v>-0.00815269779470125</v>
+        <v>7836488</v>
       </c>
       <c r="D48">
-        <v>0.1027852988770107</v>
+        <v>8396864</v>
       </c>
       <c r="E48">
-        <v>0.058806523182890855</v>
+        <v>8790154</v>
       </c>
     </row>
     <row r="49">
@@ -2746,16 +1222,16 @@
         <v>Expenses and Income</v>
       </c>
       <c r="B49" t="str">
-        <v>Investment Income</v>
+        <v>Invested Assets</v>
       </c>
       <c r="C49">
-        <v>-151620</v>
+        <v>40202154</v>
       </c>
       <c r="D49">
-        <v>2185506</v>
+        <v>46681431</v>
       </c>
       <c r="E49">
-        <v>1542857</v>
+        <v>58853678</v>
       </c>
     </row>
     <row r="50">
@@ -2763,50 +1239,50 @@
         <v>Expenses and Income</v>
       </c>
       <c r="B50" t="str">
-        <v>Net Income</v>
+        <v>Investment Return Rate</v>
       </c>
       <c r="C50">
-        <v>2139475</v>
+        <v>-0.00815269779470125</v>
       </c>
       <c r="D50">
-        <v>4124400</v>
+        <v>0.10278529887701068</v>
       </c>
       <c r="E50">
-        <v>3071666</v>
+        <v>0.05880652318289086</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Reserves</v>
+        <v>Expenses and Income</v>
       </c>
       <c r="B51" t="str">
-        <v>Prior-Year Development</v>
+        <v>Investment Income</v>
       </c>
       <c r="C51">
-        <v>-48180</v>
+        <v>-327756</v>
       </c>
       <c r="D51">
-        <v>-349180</v>
+        <v>4798165</v>
       </c>
       <c r="E51">
-        <v>-139087</v>
+        <v>3460980</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Reserves</v>
+        <v>Expenses and Income</v>
       </c>
       <c r="B52" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Net Income</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>1767646</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>10252799</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>13229199</v>
       </c>
     </row>
     <row r="53">
@@ -2814,16 +1290,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Prior-Year Development</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>-474922</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>-508073</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>-345608</v>
       </c>
     </row>
     <row r="54">
@@ -2831,16 +1307,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>17099067</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>22293895</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>24544287</v>
       </c>
     </row>
     <row r="55">
@@ -2848,16 +1324,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>10870802</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>9723008</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>7855307</v>
       </c>
     </row>
     <row r="56">
@@ -2865,16 +1341,16 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C56">
-        <v>NaN</v>
+        <v>13398098</v>
       </c>
       <c r="D56">
-        <v>NaN</v>
+        <v>14462694</v>
       </c>
       <c r="E56">
-        <v>NaN</v>
+        <v>13948335</v>
       </c>
     </row>
     <row r="57">
@@ -2882,16 +1358,16 @@
         <v>Reserves</v>
       </c>
       <c r="B57" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C57">
-        <v>NaN</v>
+        <v>22293895</v>
       </c>
       <c r="D57">
-        <v>NaN</v>
+        <v>24544287</v>
       </c>
       <c r="E57">
-        <v>NaN</v>
+        <v>24033739</v>
       </c>
     </row>
     <row r="58">
@@ -2902,13 +1378,13 @@
         <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C58">
-        <v>8353677</v>
+        <v>22293895</v>
       </c>
       <c r="D58">
-        <v>9300939</v>
+        <v>24544287</v>
       </c>
       <c r="E58">
-        <v>10431290</v>
+        <v>24033739</v>
       </c>
     </row>
     <row r="59">
@@ -2919,13 +1395,13 @@
         <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C59">
-        <v>11244050</v>
+        <v>30007583</v>
       </c>
       <c r="D59">
-        <v>12519064</v>
+        <v>33036611</v>
       </c>
       <c r="E59">
-        <v>14040516</v>
+        <v>32349413</v>
       </c>
     </row>
     <row r="60">
@@ -2936,13 +1412,13 @@
         <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C60">
-        <v>7944347</v>
+        <v>21201494</v>
       </c>
       <c r="D60">
-        <v>8845193</v>
+        <v>23341617</v>
       </c>
       <c r="E60">
-        <v>9920156</v>
+        <v>22856086</v>
       </c>
     </row>
     <row r="61">
@@ -2953,13 +1429,13 @@
         <v>Beginning Cash</v>
       </c>
       <c r="C61">
-        <v>1595451</v>
+        <v>4144849</v>
       </c>
       <c r="D61">
-        <v>1772163</v>
+        <v>4628046</v>
       </c>
       <c r="E61">
-        <v>1871144</v>
+        <v>4958991</v>
       </c>
     </row>
     <row r="62">
@@ -2970,13 +1446,13 @@
         <v>Ending Cash</v>
       </c>
       <c r="C62">
-        <v>1771934</v>
+        <v>4628046</v>
       </c>
       <c r="D62">
-        <v>1870504</v>
+        <v>4958991</v>
       </c>
       <c r="E62">
-        <v>1974558</v>
+        <v>5191258</v>
       </c>
     </row>
     <row r="63">
@@ -2987,13 +1463,13 @@
         <v>Beginning Investments</v>
       </c>
       <c r="C63">
-        <v>18597505</v>
+        <v>40202154</v>
       </c>
       <c r="D63">
-        <v>21262826</v>
+        <v>46681431</v>
       </c>
       <c r="E63">
-        <v>26236146</v>
+        <v>58853678</v>
       </c>
     </row>
     <row r="64">
@@ -3004,13 +1480,13 @@
         <v>Ending Investments</v>
       </c>
       <c r="C64">
-        <v>21262826</v>
+        <v>46681431</v>
       </c>
       <c r="D64">
-        <v>26236146</v>
+        <v>58853678</v>
       </c>
       <c r="E64">
-        <v>30334749</v>
+        <v>71340061</v>
       </c>
     </row>
     <row r="65">
@@ -3021,13 +1497,13 @@
         <v>Other Assets</v>
       </c>
       <c r="C65">
-        <v>195188</v>
+        <v>507083</v>
       </c>
       <c r="D65">
-        <v>194171</v>
+        <v>507083</v>
       </c>
       <c r="E65">
-        <v>191334</v>
+        <v>507083</v>
       </c>
     </row>
     <row r="66">
@@ -3038,13 +1514,13 @@
         <v>Total Assets</v>
       </c>
       <c r="C66">
-        <v>23229948</v>
+        <v>51816559</v>
       </c>
       <c r="D66">
-        <v>28300822</v>
+        <v>64319751</v>
       </c>
       <c r="E66">
-        <v>32500641</v>
+        <v>77038402</v>
       </c>
     </row>
     <row r="67">
@@ -3072,13 +1548,13 @@
         <v>Other Liabilities</v>
       </c>
       <c r="C68">
-        <v>151174</v>
+        <v>392736</v>
       </c>
       <c r="D68">
-        <v>150386</v>
+        <v>392736</v>
       </c>
       <c r="E68">
-        <v>148189</v>
+        <v>392736</v>
       </c>
     </row>
     <row r="69">
@@ -3089,13 +1565,13 @@
         <v>Total Liabilities</v>
       </c>
       <c r="C69">
-        <v>8504851</v>
+        <v>22686631</v>
       </c>
       <c r="D69">
-        <v>9451325</v>
+        <v>24937024</v>
       </c>
       <c r="E69">
-        <v>10579478</v>
+        <v>24426476</v>
       </c>
     </row>
     <row r="70">
@@ -3106,13 +1582,13 @@
         <v>Beginning Surplus</v>
       </c>
       <c r="C70">
-        <v>12585622</v>
+        <v>27362282</v>
       </c>
       <c r="D70">
-        <v>14725097</v>
+        <v>29129928</v>
       </c>
       <c r="E70">
-        <v>18849497</v>
+        <v>39382727</v>
       </c>
     </row>
     <row r="71">
@@ -3123,13 +1599,13 @@
         <v>Surplus from Income</v>
       </c>
       <c r="C71">
-        <v>14725097</v>
+        <v>29129928</v>
       </c>
       <c r="D71">
-        <v>18849497</v>
+        <v>39382727</v>
       </c>
       <c r="E71">
-        <v>21921163</v>
+        <v>52611927</v>
       </c>
     </row>
     <row r="72">
@@ -3140,13 +1616,13 @@
         <v>Ending Surplus</v>
       </c>
       <c r="C72">
-        <v>14725097</v>
+        <v>29129928</v>
       </c>
       <c r="D72">
-        <v>18849497</v>
+        <v>39382727</v>
       </c>
       <c r="E72">
-        <v>21921163</v>
+        <v>52611927</v>
       </c>
     </row>
     <row r="73">
@@ -3242,7 +1718,7 @@
         <v>Expected Loss Ratio</v>
       </c>
       <c r="C78">
-        <v>0.6684491978609624</v>
+        <v>0.6684491978609625</v>
       </c>
       <c r="D78">
         <v>0.6684491978609626</v>
@@ -3259,7 +1735,7 @@
         <v>Expected Expense Ratio</v>
       </c>
       <c r="C79">
-        <v>0.33155080213903765</v>
+        <v>0.33155080213903754</v>
       </c>
       <c r="D79">
         <v>0.3315508021390374</v>
@@ -3293,13 +1769,13 @@
         <v>Actual Loss Ratio</v>
       </c>
       <c r="C81">
-        <v>0.47658261895766835</v>
+        <v>0.602616976221083</v>
       </c>
       <c r="D81">
-        <v>0.5150468947680041</v>
+        <v>0.5055389508243922</v>
       </c>
       <c r="E81">
-        <v>0.5543931247661993</v>
+        <v>0.38828119055952354</v>
       </c>
     </row>
     <row r="82">
@@ -3316,7 +1792,7 @@
         <v>0.3294687740591459</v>
       </c>
       <c r="E82">
-        <v>0.32946877405914593</v>
+        <v>0.3294687740591459</v>
       </c>
     </row>
     <row r="83">
@@ -3327,13 +1803,13 @@
         <v>Actual Combined Ratio</v>
       </c>
       <c r="C83">
-        <v>0.8060513930168142</v>
+        <v>0.9320857502802289</v>
       </c>
       <c r="D83">
-        <v>0.84451566882715</v>
+        <v>0.835007724883538</v>
       </c>
       <c r="E83">
-        <v>0.8838618988253453</v>
+        <v>0.7177499646186694</v>
       </c>
     </row>
     <row r="84">
@@ -3344,13 +1820,13 @@
         <v>Surplus</v>
       </c>
       <c r="C84">
-        <v>14725097</v>
+        <v>29129928</v>
       </c>
       <c r="D84">
-        <v>18849497</v>
+        <v>39382727</v>
       </c>
       <c r="E84">
-        <v>21921163</v>
+        <v>52611927</v>
       </c>
     </row>
     <row r="85">
@@ -3361,13 +1837,13 @@
         <v>Excess Available Surplus</v>
       </c>
       <c r="C85">
-        <v>6780750</v>
+        <v>7928434</v>
       </c>
       <c r="D85">
-        <v>10004304</v>
+        <v>16041110</v>
       </c>
       <c r="E85">
-        <v>12001006</v>
+        <v>29755841</v>
       </c>
     </row>
     <row r="86">
@@ -3378,13 +1854,13 @@
         <v>Excess Capital Ratio</v>
       </c>
       <c r="C86">
-        <v>0.8535313651626407</v>
+        <v>0.37395636433843166</v>
       </c>
       <c r="D86">
-        <v>1.1310441435261138</v>
+        <v>0.687232153357253</v>
       </c>
       <c r="E86">
-        <v>1.209759772584394</v>
+        <v>1.3018782195620995</v>
       </c>
     </row>
     <row r="87">
@@ -3411,9 +1887,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3627,13 +2103,13 @@
         <v>Active Members</v>
       </c>
       <c r="C13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -3644,13 +2120,13 @@
         <v>New Members</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3667,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3678,13 +2154,13 @@
         <v>Member Retention Rate</v>
       </c>
       <c r="C16">
-        <v>0.969</v>
+        <v>0.964</v>
       </c>
       <c r="D16">
-        <v>0.971</v>
+        <v>0.964</v>
       </c>
       <c r="E16">
-        <v>0.943</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="17">
@@ -3695,13 +2171,13 @@
         <v>Member Satisfaction</v>
       </c>
       <c r="C17">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="D17">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="E17">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="18">
@@ -3712,13 +2188,13 @@
         <v>Average Risk Quality</v>
       </c>
       <c r="C18">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="D18">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="E18">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="19">
@@ -3746,13 +2222,13 @@
         <v>Active Payroll Exposure ($M)</v>
       </c>
       <c r="C20">
-        <v>86.15</v>
+        <v>66.24</v>
       </c>
       <c r="D20">
-        <v>88.25</v>
+        <v>66.24</v>
       </c>
       <c r="E20">
-        <v>87.07</v>
+        <v>66.24</v>
       </c>
     </row>
     <row r="21">
@@ -3780,13 +2256,13 @@
         <v>Market Share</v>
       </c>
       <c r="C22">
-        <v>1.3006</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>1.3323</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>1.3145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -3814,13 +2290,13 @@
         <v>Pure Premium Rate per $100 Payroll</v>
       </c>
       <c r="C24">
-        <v>11.1216</v>
+        <v>8.9738</v>
       </c>
       <c r="D24">
-        <v>11.7403</v>
+        <v>9.473</v>
       </c>
       <c r="E24">
-        <v>12.3934</v>
+        <v>9.9999</v>
       </c>
     </row>
     <row r="25">
@@ -3831,13 +2307,13 @@
         <v>Pool Premium Rate at Selected CLF</v>
       </c>
       <c r="C25">
-        <v>14.969676464957423</v>
+        <v>12.07868926280107</v>
       </c>
       <c r="D25">
-        <v>15.802417844974238</v>
+        <v>12.75060921972499</v>
       </c>
       <c r="E25">
-        <v>16.68148341961314</v>
+        <v>13.459907108864044</v>
       </c>
     </row>
     <row r="26">
@@ -3848,13 +2324,13 @@
         <v>Gross Premium &amp; Admin Expense Rate per $100</v>
       </c>
       <c r="C26">
-        <v>22.1018</v>
+        <v>17.8335</v>
       </c>
       <c r="D26">
-        <v>23.3313</v>
+        <v>18.8255</v>
       </c>
       <c r="E26">
-        <v>24.6292</v>
+        <v>19.8728</v>
       </c>
     </row>
     <row r="27">
@@ -3865,13 +2341,13 @@
         <v>Written Payroll ($M)</v>
       </c>
       <c r="C27">
-        <v>86.15</v>
+        <v>66.24</v>
       </c>
       <c r="D27">
-        <v>88.25</v>
+        <v>66.24</v>
       </c>
       <c r="E27">
-        <v>87.07</v>
+        <v>66.24</v>
       </c>
     </row>
     <row r="28">
@@ -3882,13 +2358,13 @@
         <v>Pure Premium</v>
       </c>
       <c r="C28">
-        <v>9581260</v>
+        <v>5944223</v>
       </c>
       <c r="D28">
-        <v>10360798</v>
+        <v>6274891</v>
       </c>
       <c r="E28">
-        <v>10790912</v>
+        <v>6623954</v>
       </c>
     </row>
     <row r="29">
@@ -3899,13 +2375,13 @@
         <v>Pool Premium at Selected CLF</v>
       </c>
       <c r="C29">
-        <v>12896376</v>
+        <v>8000924</v>
       </c>
       <c r="D29">
-        <v>13945634</v>
+        <v>8446004</v>
       </c>
       <c r="E29">
-        <v>14524568</v>
+        <v>8915842</v>
       </c>
     </row>
     <row r="30">
@@ -3916,13 +2392,13 @@
         <v>Admin Expense</v>
       </c>
       <c r="C30">
-        <v>1437189</v>
+        <v>891633</v>
       </c>
       <c r="D30">
-        <v>1554120</v>
+        <v>941234</v>
       </c>
       <c r="E30">
-        <v>1618637</v>
+        <v>993593</v>
       </c>
     </row>
     <row r="31">
@@ -3933,13 +2409,13 @@
         <v>Gross Premium &amp; Admin Expense</v>
       </c>
       <c r="C31">
-        <v>19040743</v>
+        <v>11812894</v>
       </c>
       <c r="D31">
-        <v>20589910</v>
+        <v>12470029</v>
       </c>
       <c r="E31">
-        <v>21444672</v>
+        <v>13163718</v>
       </c>
     </row>
     <row r="32">
@@ -3984,13 +2460,13 @@
         <v>Pure Premium</v>
       </c>
       <c r="C34">
-        <v>9581260</v>
+        <v>5944223</v>
       </c>
       <c r="D34">
-        <v>10360798</v>
+        <v>6274891</v>
       </c>
       <c r="E34">
-        <v>10790912</v>
+        <v>6623954</v>
       </c>
     </row>
     <row r="35">
@@ -4001,13 +2477,13 @@
         <v>Pool Premium at Selected CLF</v>
       </c>
       <c r="C35">
-        <v>12896376</v>
+        <v>8000924</v>
       </c>
       <c r="D35">
-        <v>13945634</v>
+        <v>8446004</v>
       </c>
       <c r="E35">
-        <v>14524568</v>
+        <v>8915842</v>
       </c>
     </row>
     <row r="36">
@@ -4018,13 +2494,13 @@
         <v>Member-Level Simulated Loss incl. Shared Events</v>
       </c>
       <c r="C36">
-        <v>14215729</v>
+        <v>5581640</v>
       </c>
       <c r="D36">
-        <v>10131544</v>
+        <v>6073469</v>
       </c>
       <c r="E36">
-        <v>5933391</v>
+        <v>7158788</v>
       </c>
     </row>
     <row r="37">
@@ -4035,13 +2511,13 @@
         <v>Shared Annual Loss Factor</v>
       </c>
       <c r="C37">
-        <v>1.372454361221214</v>
+        <v>1.1049503865330403</v>
       </c>
       <c r="D37">
-        <v>1.2306491311831955</v>
+        <v>1.1103116094116727</v>
       </c>
       <c r="E37">
-        <v>0.6776919118144195</v>
+        <v>1.0060010545881324</v>
       </c>
     </row>
     <row r="38">
@@ -4086,13 +2562,13 @@
         <v>Gross Ultimate Loss + LAE</v>
       </c>
       <c r="C40">
-        <v>14215729</v>
+        <v>5581640</v>
       </c>
       <c r="D40">
-        <v>10131544</v>
+        <v>6073469</v>
       </c>
       <c r="E40">
-        <v>5933391</v>
+        <v>7158788</v>
       </c>
     </row>
     <row r="41">
@@ -4120,7 +2596,7 @@
         <v>Reinsurance Recovery</v>
       </c>
       <c r="C42">
-        <v>1679365</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4137,13 +2613,13 @@
         <v>Net Ultimate Loss + LAE</v>
       </c>
       <c r="C43">
-        <v>12536364</v>
+        <v>5581640</v>
       </c>
       <c r="D43">
-        <v>10131544</v>
+        <v>6073469</v>
       </c>
       <c r="E43">
-        <v>5933391</v>
+        <v>7158788</v>
       </c>
     </row>
     <row r="44">
@@ -4154,13 +2630,13 @@
         <v>Operating Expense</v>
       </c>
       <c r="C44">
-        <v>1437189</v>
+        <v>891633</v>
       </c>
       <c r="D44">
-        <v>1554120</v>
+        <v>941234</v>
       </c>
       <c r="E44">
-        <v>1618637</v>
+        <v>993593</v>
       </c>
     </row>
     <row r="45">
@@ -4188,13 +2664,13 @@
         <v>Reinsurance Cost</v>
       </c>
       <c r="C46">
-        <v>4836141</v>
+        <v>3000346</v>
       </c>
       <c r="D46">
-        <v>5229613</v>
+        <v>3167251</v>
       </c>
       <c r="E46">
-        <v>5446713</v>
+        <v>3343441</v>
       </c>
     </row>
     <row r="47">
@@ -4205,13 +2681,13 @@
         <v>Invested Assets</v>
       </c>
       <c r="C47">
-        <v>21604649</v>
+        <v>18597505</v>
       </c>
       <c r="D47">
-        <v>25418606</v>
+        <v>21262826</v>
       </c>
       <c r="E47">
-        <v>32617531</v>
+        <v>26236146</v>
       </c>
     </row>
     <row r="48">
@@ -4239,13 +2715,13 @@
         <v>Investment Income</v>
       </c>
       <c r="C49">
-        <v>-176136</v>
+        <v>-151620</v>
       </c>
       <c r="D49">
-        <v>2612659</v>
+        <v>2185506</v>
       </c>
       <c r="E49">
-        <v>1918124</v>
+        <v>1542857</v>
       </c>
     </row>
     <row r="50">
@@ -4256,13 +2732,13 @@
         <v>Net Income</v>
       </c>
       <c r="C50">
-        <v>-371829</v>
+        <v>2139475</v>
       </c>
       <c r="D50">
-        <v>6128399</v>
+        <v>4124400</v>
       </c>
       <c r="E50">
-        <v>10157534</v>
+        <v>3071666</v>
       </c>
     </row>
     <row r="51">
@@ -4273,13 +2749,13 @@
         <v>Prior-Year Development</v>
       </c>
       <c r="C51">
-        <v>-426742</v>
+        <v>-48180</v>
       </c>
       <c r="D51">
-        <v>-158893</v>
+        <v>-349180</v>
       </c>
       <c r="E51">
-        <v>-206521</v>
+        <v>-139087</v>
       </c>
     </row>
     <row r="52">
@@ -4287,16 +2763,16 @@
         <v>Reserves</v>
       </c>
       <c r="B52" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>7651348</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
     </row>
     <row r="53">
@@ -4304,16 +2780,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>3348984</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>3644082</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>4295273</v>
       </c>
     </row>
     <row r="54">
@@ -4321,16 +2797,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>4927491</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>5475388</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>6167524</v>
       </c>
     </row>
     <row r="55">
@@ -4338,16 +2814,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>10431290</v>
       </c>
     </row>
     <row r="56">
@@ -4355,16 +2831,16 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C56">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D56">
-        <v>NaN</v>
+        <v>9300939</v>
       </c>
       <c r="E56">
-        <v>NaN</v>
+        <v>10431290</v>
       </c>
     </row>
     <row r="57">
@@ -4372,16 +2848,16 @@
         <v>Reserves</v>
       </c>
       <c r="B57" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C57">
-        <v>NaN</v>
+        <v>11244050</v>
       </c>
       <c r="D57">
-        <v>NaN</v>
+        <v>12519064</v>
       </c>
       <c r="E57">
-        <v>NaN</v>
+        <v>14040516</v>
       </c>
     </row>
     <row r="58">
@@ -4389,50 +2865,50 @@
         <v>Reserves</v>
       </c>
       <c r="B58" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C58">
-        <v>13940218</v>
+        <v>7944347</v>
       </c>
       <c r="D58">
-        <v>15243348</v>
+        <v>8845193</v>
       </c>
       <c r="E58">
-        <v>13602450</v>
+        <v>9920156</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B59" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C59">
-        <v>18763533</v>
+        <v>1595451</v>
       </c>
       <c r="D59">
-        <v>20517547</v>
+        <v>1772163</v>
       </c>
       <c r="E59">
-        <v>18308897</v>
+        <v>1871144</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B60" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C60">
-        <v>13257147</v>
+        <v>1771934</v>
       </c>
       <c r="D60">
-        <v>14496424</v>
+        <v>1870504</v>
       </c>
       <c r="E60">
-        <v>12935930</v>
+        <v>1974558</v>
       </c>
     </row>
     <row r="61">
@@ -4440,16 +2916,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B61" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C61">
-        <v>2549399</v>
+        <v>18597505</v>
       </c>
       <c r="D61">
-        <v>2855882</v>
+        <v>21262826</v>
       </c>
       <c r="E61">
-        <v>3087847</v>
+        <v>26236146</v>
       </c>
     </row>
     <row r="62">
@@ -4457,16 +2933,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B62" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C62">
-        <v>2856111</v>
+        <v>21262826</v>
       </c>
       <c r="D62">
-        <v>3088486</v>
+        <v>26236146</v>
       </c>
       <c r="E62">
-        <v>3216701</v>
+        <v>30334749</v>
       </c>
     </row>
     <row r="63">
@@ -4474,16 +2950,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B63" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C63">
-        <v>21604649</v>
+        <v>195188</v>
       </c>
       <c r="D63">
-        <v>25418606</v>
+        <v>194171</v>
       </c>
       <c r="E63">
-        <v>32617531</v>
+        <v>191334</v>
       </c>
     </row>
     <row r="64">
@@ -4491,16 +2967,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B64" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C64">
-        <v>25418606</v>
+        <v>23229948</v>
       </c>
       <c r="D64">
-        <v>32617531</v>
+        <v>28300822</v>
       </c>
       <c r="E64">
-        <v>41005312</v>
+        <v>32500641</v>
       </c>
     </row>
     <row r="65">
@@ -4508,16 +2984,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C65">
-        <v>311894</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>312911</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>315748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4525,16 +3001,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C66">
-        <v>28586611</v>
+        <v>151174</v>
       </c>
       <c r="D66">
-        <v>36018929</v>
+        <v>150386</v>
       </c>
       <c r="E66">
-        <v>44537761</v>
+        <v>148189</v>
       </c>
     </row>
     <row r="67">
@@ -4542,16 +3018,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>8504851</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>9451325</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>10579478</v>
       </c>
     </row>
     <row r="68">
@@ -4559,16 +3035,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C68">
-        <v>241563</v>
+        <v>12585622</v>
       </c>
       <c r="D68">
-        <v>242350</v>
+        <v>14725097</v>
       </c>
       <c r="E68">
-        <v>244548</v>
+        <v>18849497</v>
       </c>
     </row>
     <row r="69">
@@ -4576,16 +3052,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C69">
-        <v>14181780</v>
+        <v>14725097</v>
       </c>
       <c r="D69">
-        <v>15485699</v>
+        <v>18849497</v>
       </c>
       <c r="E69">
-        <v>13846997</v>
+        <v>21921163</v>
       </c>
     </row>
     <row r="70">
@@ -4593,16 +3069,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B70" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C70">
-        <v>14776660</v>
+        <v>14725097</v>
       </c>
       <c r="D70">
-        <v>14404831</v>
+        <v>18849497</v>
       </c>
       <c r="E70">
-        <v>20533230</v>
+        <v>21921163</v>
       </c>
     </row>
     <row r="71">
@@ -4610,41 +3086,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B71" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C71">
-        <v>14404831</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>20533230</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>30690764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B72" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C72">
-        <v>14404831</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>20533230</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>30690764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B73" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -4661,7 +3137,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B74" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -4678,7 +3154,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B75" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -4692,36 +3168,36 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B76" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.6684491978609624</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B77" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.33155080213903765</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
     </row>
     <row r="78">
@@ -4729,16 +3205,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B78" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C78">
-        <v>0.6684491978609625</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4746,16 +3222,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B79" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C79">
-        <v>0.33155080213903754</v>
+        <v>0.47658261895766835</v>
       </c>
       <c r="D79">
-        <v>0.3315508021390374</v>
+        <v>0.5150468947680041</v>
       </c>
       <c r="E79">
-        <v>0.3315508021390374</v>
+        <v>0.5543931247661993</v>
       </c>
     </row>
     <row r="80">
@@ -4763,16 +3239,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B80" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.32946877405914593</v>
       </c>
     </row>
     <row r="81">
@@ -4780,16 +3256,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B81" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C81">
-        <v>0.6808088080275256</v>
+        <v>0.8060513930168142</v>
       </c>
       <c r="D81">
-        <v>0.4997805801598653</v>
+        <v>0.84451566882715</v>
       </c>
       <c r="E81">
-        <v>0.2863141043778507</v>
+        <v>0.8838618988253453</v>
       </c>
     </row>
     <row r="82">
@@ -4797,16 +3273,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C82">
-        <v>0.3294687740591458</v>
+        <v>14725097</v>
       </c>
       <c r="D82">
-        <v>0.3294687740591458</v>
+        <v>18849497</v>
       </c>
       <c r="E82">
-        <v>0.3294687740591459</v>
+        <v>21921163</v>
       </c>
     </row>
     <row r="83">
@@ -4814,16 +3290,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C83">
-        <v>1.0102775820866714</v>
+        <v>6780750</v>
       </c>
       <c r="D83">
-        <v>0.8292493542190111</v>
+        <v>10004304</v>
       </c>
       <c r="E83">
-        <v>0.6157828784369965</v>
+        <v>12001006</v>
       </c>
     </row>
     <row r="84">
@@ -4831,16 +3307,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B84" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C84">
-        <v>14404831</v>
+        <v>0.8535313651626407</v>
       </c>
       <c r="D84">
-        <v>20533230</v>
+        <v>1.1310441435261138</v>
       </c>
       <c r="E84">
-        <v>30690764</v>
+        <v>1.209759772584394</v>
       </c>
     </row>
     <row r="85">
@@ -4848,55 +3324,1477 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B85" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C85">
-        <v>1147684</v>
-      </c>
-      <c r="D85">
-        <v>6036806</v>
-      </c>
-      <c r="E85">
-        <v>17754834</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C86">
-        <v>0.08657097262107838</v>
-      </c>
-      <c r="D86">
-        <v>0.4164341511604685</v>
-      </c>
-      <c r="E86">
-        <v>1.3725209512423653</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B87" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C87" t="str">
-        <v>Adequate</v>
-      </c>
-      <c r="D87" t="str">
+      <c r="C85" t="str">
         <v>Strong</v>
       </c>
-      <c r="E87" t="str">
+      <c r="D85" t="str">
+        <v>Strong</v>
+      </c>
+      <c r="E85" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E85"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Metric</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Year 1 / 2026</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Year 2 / 2027</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Year 3 / 2028</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Year</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Year Number</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Year</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Calendar Year</v>
+      </c>
+      <c r="C3">
+        <v>2026</v>
+      </c>
+      <c r="D3">
+        <v>2027</v>
+      </c>
+      <c r="E3">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Rate Change</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Funding Confidence Level</v>
+      </c>
+      <c r="C5">
+        <v>0.75</v>
+      </c>
+      <c r="D5">
+        <v>0.75</v>
+      </c>
+      <c r="E5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Selected CLF</v>
+      </c>
+      <c r="C6">
+        <v>1.346</v>
+      </c>
+      <c r="D6">
+        <v>1.346</v>
+      </c>
+      <c r="E6">
+        <v>1.346</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Dividend %</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Assessment %</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Underwriting Strictness</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Risk Control %</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Reinsurance Level</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Decisions</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Asset Allocation</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Cash 10% / Bonds 80% / Equities 10%</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Cash 10% / Bonds 80% / Equities 10%</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Cash 10% / Bonds 80% / Equities 10%</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Active Members</v>
+      </c>
+      <c r="C13">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B14" t="str">
+        <v>New Members</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Withdrawn Members</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Member Retention Rate</v>
+      </c>
+      <c r="C16">
+        <v>0.969</v>
+      </c>
+      <c r="D16">
+        <v>0.971</v>
+      </c>
+      <c r="E16">
+        <v>0.943</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Member Satisfaction</v>
+      </c>
+      <c r="C17">
+        <v>7.9</v>
+      </c>
+      <c r="D17">
+        <v>7.9</v>
+      </c>
+      <c r="E17">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Average Risk Quality</v>
+      </c>
+      <c r="C18">
+        <v>4.6</v>
+      </c>
+      <c r="D18">
+        <v>4.6</v>
+      </c>
+      <c r="E18">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Exposure Basis</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Payroll ($M)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Payroll ($M)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Payroll ($M)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Active Payroll Exposure ($M)</v>
+      </c>
+      <c r="C20">
+        <v>86.15</v>
+      </c>
+      <c r="D20">
+        <v>88.25</v>
+      </c>
+      <c r="E20">
+        <v>87.07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Total Market Payroll ($M)</v>
+      </c>
+      <c r="C21">
+        <v>66.24</v>
+      </c>
+      <c r="D21">
+        <v>66.24</v>
+      </c>
+      <c r="E21">
+        <v>66.24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Membership</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Market Share</v>
+      </c>
+      <c r="C22">
+        <v>1.3006</v>
+      </c>
+      <c r="D22">
+        <v>1.3323</v>
+      </c>
+      <c r="E22">
+        <v>1.3145</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Rate Level Index</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Pure Premium Rate per $100 Payroll</v>
+      </c>
+      <c r="C24">
+        <v>11.1216</v>
+      </c>
+      <c r="D24">
+        <v>11.7403</v>
+      </c>
+      <c r="E24">
+        <v>12.3934</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Pool Premium Rate at Selected CLF</v>
+      </c>
+      <c r="C25">
+        <v>14.969676464957423</v>
+      </c>
+      <c r="D25">
+        <v>15.802417844974238</v>
+      </c>
+      <c r="E25">
+        <v>16.68148341961314</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Gross Premium &amp; Admin Expense Rate per $100</v>
+      </c>
+      <c r="C26">
+        <v>22.1018</v>
+      </c>
+      <c r="D26">
+        <v>23.3313</v>
+      </c>
+      <c r="E26">
+        <v>24.6292</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Written Payroll ($M)</v>
+      </c>
+      <c r="C27">
+        <v>86.15</v>
+      </c>
+      <c r="D27">
+        <v>88.25</v>
+      </c>
+      <c r="E27">
+        <v>87.07</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Pure Premium</v>
+      </c>
+      <c r="C28">
+        <v>9581260</v>
+      </c>
+      <c r="D28">
+        <v>10360798</v>
+      </c>
+      <c r="E28">
+        <v>10790912</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Pool Premium at Selected CLF</v>
+      </c>
+      <c r="C29">
+        <v>12896376</v>
+      </c>
+      <c r="D29">
+        <v>13945634</v>
+      </c>
+      <c r="E29">
+        <v>14524568</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Admin Expense</v>
+      </c>
+      <c r="C30">
+        <v>1437189</v>
+      </c>
+      <c r="D30">
+        <v>1554120</v>
+      </c>
+      <c r="E30">
+        <v>1618637</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Gross Premium &amp; Admin Expense</v>
+      </c>
+      <c r="C31">
+        <v>19040743</v>
+      </c>
+      <c r="D31">
+        <v>20589910</v>
+      </c>
+      <c r="E31">
+        <v>21444672</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Assessments</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Rate and Premium</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Dividends / Returned Pool Premium</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Pure Premium</v>
+      </c>
+      <c r="C34">
+        <v>9581260</v>
+      </c>
+      <c r="D34">
+        <v>10360798</v>
+      </c>
+      <c r="E34">
+        <v>10790912</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Pool Premium at Selected CLF</v>
+      </c>
+      <c r="C35">
+        <v>12896376</v>
+      </c>
+      <c r="D35">
+        <v>13945634</v>
+      </c>
+      <c r="E35">
+        <v>14524568</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Member-Level Simulated Loss incl. Shared Events</v>
+      </c>
+      <c r="C36">
+        <v>14215729</v>
+      </c>
+      <c r="D36">
+        <v>10131544</v>
+      </c>
+      <c r="E36">
+        <v>5933391</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Shared Annual Loss Factor</v>
+      </c>
+      <c r="C37">
+        <v>1.372454361221214</v>
+      </c>
+      <c r="D37">
+        <v>1.2306491311831955</v>
+      </c>
+      <c r="E37">
+        <v>0.6776919118144195</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Catastrophe Factor</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Shock Uplift (included in simulated loss)</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Gross Ultimate Loss + LAE</v>
+      </c>
+      <c r="C40">
+        <v>14215729</v>
+      </c>
+      <c r="D40">
+        <v>10131544</v>
+      </c>
+      <c r="E40">
+        <v>5933391</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Shock Loss Incurred</v>
+      </c>
+      <c r="C41" t="str">
+        <v>No</v>
+      </c>
+      <c r="D41" t="str">
+        <v>No</v>
+      </c>
+      <c r="E41" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Reinsurance Recovery</v>
+      </c>
+      <c r="C42">
+        <v>1679365</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Losses</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Net Ultimate Loss + LAE</v>
+      </c>
+      <c r="C43">
+        <v>12536364</v>
+      </c>
+      <c r="D43">
+        <v>10131544</v>
+      </c>
+      <c r="E43">
+        <v>5933391</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Operating Expense</v>
+      </c>
+      <c r="C44">
+        <v>1437189</v>
+      </c>
+      <c r="D44">
+        <v>1554120</v>
+      </c>
+      <c r="E44">
+        <v>1618637</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Risk Control Investment</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Reinsurance Cost</v>
+      </c>
+      <c r="C46">
+        <v>4836141</v>
+      </c>
+      <c r="D46">
+        <v>5229613</v>
+      </c>
+      <c r="E46">
+        <v>5446713</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Invested Assets</v>
+      </c>
+      <c r="C47">
+        <v>21604649</v>
+      </c>
+      <c r="D47">
+        <v>25418606</v>
+      </c>
+      <c r="E47">
+        <v>32617531</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Investment Return Rate</v>
+      </c>
+      <c r="C48">
+        <v>-0.00815269779470125</v>
+      </c>
+      <c r="D48">
+        <v>0.1027852988770107</v>
+      </c>
+      <c r="E48">
+        <v>0.058806523182890855</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Investment Income</v>
+      </c>
+      <c r="C49">
+        <v>-176136</v>
+      </c>
+      <c r="D49">
+        <v>2612659</v>
+      </c>
+      <c r="E49">
+        <v>1918124</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Expenses and Income</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Net Income</v>
+      </c>
+      <c r="C50">
+        <v>-371829</v>
+      </c>
+      <c r="D50">
+        <v>6128399</v>
+      </c>
+      <c r="E50">
+        <v>10157534</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Prior-Year Development</v>
+      </c>
+      <c r="C51">
+        <v>-426742</v>
+      </c>
+      <c r="D51">
+        <v>-158893</v>
+      </c>
+      <c r="E51">
+        <v>-206521</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Beginning Net Reserve</v>
+      </c>
+      <c r="C52">
+        <v>9447719</v>
+      </c>
+      <c r="D52">
+        <v>13940218</v>
+      </c>
+      <c r="E52">
+        <v>15243348</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Current-Year Net Reserve</v>
+      </c>
+      <c r="C53">
+        <v>7521818</v>
+      </c>
+      <c r="D53">
+        <v>6078926</v>
+      </c>
+      <c r="E53">
+        <v>3560035</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Net Paid Losses</v>
+      </c>
+      <c r="C54">
+        <v>8470607</v>
+      </c>
+      <c r="D54">
+        <v>8987306</v>
+      </c>
+      <c r="E54">
+        <v>7780811</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Ending Net Reserve</v>
+      </c>
+      <c r="C55">
+        <v>13940218</v>
+      </c>
+      <c r="D55">
+        <v>15243348</v>
+      </c>
+      <c r="E55">
+        <v>13602450</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Expected Net Unpaid Loss</v>
+      </c>
+      <c r="C56">
+        <v>13940218</v>
+      </c>
+      <c r="D56">
+        <v>15243348</v>
+      </c>
+      <c r="E56">
+        <v>13602450</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Indicated Net Reserve at Confidence</v>
+      </c>
+      <c r="C57">
+        <v>18763533</v>
+      </c>
+      <c r="D57">
+        <v>20517547</v>
+      </c>
+      <c r="E57">
+        <v>18308897</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Reserves</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Reserve Risk Margin Needed</v>
+      </c>
+      <c r="C58">
+        <v>13257147</v>
+      </c>
+      <c r="D58">
+        <v>14496424</v>
+      </c>
+      <c r="E58">
+        <v>12935930</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Beginning Cash</v>
+      </c>
+      <c r="C59">
+        <v>2549399</v>
+      </c>
+      <c r="D59">
+        <v>2855882</v>
+      </c>
+      <c r="E59">
+        <v>3087847</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Ending Cash</v>
+      </c>
+      <c r="C60">
+        <v>2856111</v>
+      </c>
+      <c r="D60">
+        <v>3088486</v>
+      </c>
+      <c r="E60">
+        <v>3216701</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Beginning Investments</v>
+      </c>
+      <c r="C61">
+        <v>21604649</v>
+      </c>
+      <c r="D61">
+        <v>25418606</v>
+      </c>
+      <c r="E61">
+        <v>32617531</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Ending Investments</v>
+      </c>
+      <c r="C62">
+        <v>25418606</v>
+      </c>
+      <c r="D62">
+        <v>32617531</v>
+      </c>
+      <c r="E62">
+        <v>41005312</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Other Assets</v>
+      </c>
+      <c r="C63">
+        <v>311894</v>
+      </c>
+      <c r="D63">
+        <v>312911</v>
+      </c>
+      <c r="E63">
+        <v>315748</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Total Assets</v>
+      </c>
+      <c r="C64">
+        <v>28586611</v>
+      </c>
+      <c r="D64">
+        <v>36018929</v>
+      </c>
+      <c r="E64">
+        <v>44537761</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Unearned Premium</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Other Liabilities</v>
+      </c>
+      <c r="C66">
+        <v>241563</v>
+      </c>
+      <c r="D66">
+        <v>242350</v>
+      </c>
+      <c r="E66">
+        <v>244548</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Total Liabilities</v>
+      </c>
+      <c r="C67">
+        <v>14181780</v>
+      </c>
+      <c r="D67">
+        <v>15485699</v>
+      </c>
+      <c r="E67">
+        <v>13846997</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Beginning Surplus</v>
+      </c>
+      <c r="C68">
+        <v>14776660</v>
+      </c>
+      <c r="D68">
+        <v>14404831</v>
+      </c>
+      <c r="E68">
+        <v>20533230</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Surplus from Income</v>
+      </c>
+      <c r="C69">
+        <v>14404831</v>
+      </c>
+      <c r="D69">
+        <v>20533230</v>
+      </c>
+      <c r="E69">
+        <v>30690764</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Ending Surplus</v>
+      </c>
+      <c r="C70">
+        <v>14404831</v>
+      </c>
+      <c r="D70">
+        <v>20533230</v>
+      </c>
+      <c r="E70">
+        <v>30690764</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Balance Sheet and Surplus</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Surplus Tie-Out Difference</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Inter-Line Loan</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Loan Originated This Year</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Inter-Line Loan</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Loan Interest Accrued</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Inter-Line Loan</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Loan Repayment Applied</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Inter-Line Loan</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Outstanding Loan Balance</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Expected Loss Ratio</v>
+      </c>
+      <c r="C76">
+        <v>0.6684491978609625</v>
+      </c>
+      <c r="D76">
+        <v>0.6684491978609626</v>
+      </c>
+      <c r="E76">
+        <v>0.6684491978609626</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Expected Expense Ratio</v>
+      </c>
+      <c r="C77">
+        <v>0.33155080213903754</v>
+      </c>
+      <c r="D77">
+        <v>0.3315508021390374</v>
+      </c>
+      <c r="E77">
+        <v>0.3315508021390374</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Expected Combined Ratio</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Actual Loss Ratio</v>
+      </c>
+      <c r="C79">
+        <v>0.6808088080275256</v>
+      </c>
+      <c r="D79">
+        <v>0.4997805801598653</v>
+      </c>
+      <c r="E79">
+        <v>0.2863141043778507</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Actual Expense Ratio</v>
+      </c>
+      <c r="C80">
+        <v>0.3294687740591458</v>
+      </c>
+      <c r="D80">
+        <v>0.3294687740591458</v>
+      </c>
+      <c r="E80">
+        <v>0.3294687740591459</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Actual Combined Ratio</v>
+      </c>
+      <c r="C81">
+        <v>1.0102775820866714</v>
+      </c>
+      <c r="D81">
+        <v>0.8292493542190111</v>
+      </c>
+      <c r="E81">
+        <v>0.6157828784369965</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Surplus</v>
+      </c>
+      <c r="C82">
+        <v>14404831</v>
+      </c>
+      <c r="D82">
+        <v>20533230</v>
+      </c>
+      <c r="E82">
+        <v>30690764</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Excess Available Surplus</v>
+      </c>
+      <c r="C83">
+        <v>1147684</v>
+      </c>
+      <c r="D83">
+        <v>6036806</v>
+      </c>
+      <c r="E83">
+        <v>17754834</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Excess Capital Ratio</v>
+      </c>
+      <c r="C84">
+        <v>0.08657097262107838</v>
+      </c>
+      <c r="D84">
+        <v>0.4164341511604685</v>
+      </c>
+      <c r="E84">
+        <v>1.3725209512423653</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Ratios and Capital</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Excess Capital Status</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Adequate</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Strong</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Strong</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>